--- a/data/trans_camb/CAGE_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/CAGE_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 2,48</t>
+          <t>-0,02; 2,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,81</t>
+          <t>0,21; 2,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 9,17</t>
+          <t>2,71; 9,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,0</t>
+          <t>-0,78; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,22</t>
+          <t>-0,61; 0,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,75</t>
+          <t>-0,24; 3,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,83</t>
+          <t>-0,21; 0,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,14</t>
+          <t>-0,02; 1,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,56</t>
+          <t>2,44; 7,54</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 545,42</t>
+          <t>-20,29; 539,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 580,49</t>
+          <t>-1,66; 514,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>179,09; 1707,03</t>
+          <t>179,56; 1832,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,89; 296,18</t>
+          <t>-35,47; 308,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 398,65</t>
+          <t>-11,35; 401,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>326,59; 2236,59</t>
+          <t>331,21; 2389,46</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,13</t>
+          <t>0,55; 2,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,2</t>
+          <t>-0,07; 1,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,51</t>
+          <t>-0,37; 1,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,36</t>
+          <t>-0,33; 0,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,6</t>
+          <t>-0,15; 0,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,44</t>
+          <t>0,07; 2,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,19</t>
+          <t>0,3; 1,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 0,79</t>
+          <t>-0,01; 0,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,51</t>
+          <t>0,11; 1,43</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,33; 437,24</t>
+          <t>31,87; 387,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 226,05</t>
+          <t>-11,68; 255,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,12; 255,74</t>
+          <t>-35,61; 257,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-86,0; 372,16</t>
+          <t>-82,39; 541,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,07; 699,36</t>
+          <t>-52,78; 736,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 1908,85</t>
+          <t>-13,45; 2152,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,87; 320,29</t>
+          <t>38,83; 334,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 204,36</t>
+          <t>-2,31; 219,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,33; 350,25</t>
+          <t>11,51; 364,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,62</t>
+          <t>-0,46; 2,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,62</t>
+          <t>-0,8; 1,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,8</t>
+          <t>0,53; 3,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,0</t>
+          <t>-1,29; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,08</t>
+          <t>-0,19; 2,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,54</t>
+          <t>-0,16; 2,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,35</t>
+          <t>-0,56; 1,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 1,38</t>
+          <t>-0,23; 1,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,69</t>
+          <t>0,44; 2,78</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-9,37; inf</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-19,73; 2371,18</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-69,14; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,66; 649,67</t>
+          <t>-88,3; 539,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,67; 712,69</t>
+          <t>-38,2; 730,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,67; 1346,63</t>
+          <t>13,06; 1139,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,76</t>
+          <t>0,52; 1,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,19</t>
+          <t>0,21; 1,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,4</t>
+          <t>0,73; 2,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,08</t>
+          <t>-0,38; 0,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,52</t>
+          <t>-0,12; 0,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,12</t>
+          <t>0,24; 1,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,83</t>
+          <t>0,17; 0,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,73</t>
+          <t>0,13; 0,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,97</t>
+          <t>0,75; 1,95</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>50,54; 305,96</t>
+          <t>54,76; 321,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,22; 210,83</t>
+          <t>16,03; 203,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72,78; 396,96</t>
+          <t>64,3; 401,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-89,26; 84,27</t>
+          <t>-89,02; 66,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 362,22</t>
+          <t>-31,95; 341,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,58; 1245,17</t>
+          <t>61,73; 1173,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,02; 205,04</t>
+          <t>25,46; 198,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,1; 180,37</t>
+          <t>18,02; 194,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>109,19; 461,62</t>
+          <t>124,06; 480,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/CAGE_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/CAGE_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>4,27</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,35</t>
+          <t>-0,0; 2,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,76</t>
+          <t>0,12; 2,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 9,27</t>
+          <t>2,69; 8,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,0</t>
+          <t>-0,83; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,22</t>
+          <t>-0,6; 0,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,93</t>
+          <t>-0,24; 3,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,87</t>
+          <t>-0,21; 0,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,19</t>
+          <t>-0,03; 1,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,54</t>
+          <t>2,32; 7,08</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>605,32%</t>
+          <t>594,18%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>435,41%</t>
+          <t>400,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>878,21%</t>
+          <t>852,19%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 539,0</t>
+          <t>-12,57; 533,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 514,92</t>
+          <t>2,66; 583,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>179,56; 1832,5</t>
+          <t>195,37; 1666,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 308,48</t>
+          <t>-34,65; 313,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 401,01</t>
+          <t>-13,89; 406,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>331,21; 2389,46</t>
+          <t>330,5; 2180,42</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>1,14</t>
         </is>
       </c>
     </row>
@@ -893,37 +893,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,15</t>
+          <t>0,51; 2,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,25</t>
+          <t>-0,06; 1,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,39</t>
+          <t>-0,12; 1,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,42</t>
+          <t>-0,34; 0,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,62</t>
+          <t>-0,16; 0,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,46</t>
+          <t>0,64; 3,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,19</t>
+          <t>0,31; 1,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,43</t>
+          <t>0,49; 2,0</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>402,36%</t>
+          <t>704,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>137,69%</t>
+          <t>210,11%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,87; 387,87</t>
+          <t>43,76; 392,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 255,17</t>
+          <t>-9,65; 238,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,61; 257,75</t>
+          <t>-15,55; 314,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-82,39; 541,45</t>
+          <t>-86,59; 481,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,78; 736,16</t>
+          <t>-49,31; 821,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 2152,94</t>
+          <t>114,07; 3941,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,83; 334,63</t>
+          <t>39,08; 315,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 219,88</t>
+          <t>-2,74; 224,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,51; 364,83</t>
+          <t>57,37; 476,17</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>1,88</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,55</t>
+          <t>-0,63; 2,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,47</t>
+          <t>-0,82; 1,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,93</t>
+          <t>0,81; 4,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,0</t>
+          <t>-1,51; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,08</t>
+          <t>-0,18; 2,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,48</t>
+          <t>-0,01; 2,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,05</t>
+          <t>-0,58; 1,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,33</t>
+          <t>-0,25; 1,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,78</t>
+          <t>0,85; 3,16</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>307,53%</t>
+          <t>398,36%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>219,37%</t>
+          <t>267,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>284,22%</t>
+          <t>360,08%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,37; inf</t>
+          <t>14,37; 2314,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>-80,98; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-88,3; 539,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 730,29</t>
+          <t>-49,26; 713,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,06; 1139,52</t>
+          <t>65,67; 1194,07</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,78</t>
+          <t>0,53; 1,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,24</t>
+          <t>0,14; 1,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,45</t>
+          <t>0,93; 2,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,07</t>
+          <t>-0,42; 0,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 0,52</t>
+          <t>-0,09; 0,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,99</t>
+          <t>0,85; 2,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,79</t>
+          <t>0,19; 0,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,75</t>
+          <t>0,13; 0,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,95</t>
+          <t>1,16; 2,49</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187,89%</t>
+          <t>216,3%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>379,82%</t>
+          <t>577,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>259,42%</t>
+          <t>330,89%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>54,76; 321,59</t>
+          <t>50,44; 299,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,03; 203,36</t>
+          <t>11,11; 204,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64,3; 401,32</t>
+          <t>86,5; 445,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-89,02; 66,41</t>
+          <t>-88,03; 88,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 341,15</t>
+          <t>-29,48; 395,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,73; 1173,69</t>
+          <t>167,53; 1700,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,46; 198,71</t>
+          <t>25,19; 196,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,02; 194,17</t>
+          <t>18,21; 170,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>124,06; 480,62</t>
+          <t>181,12; 585,0</t>
         </is>
       </c>
     </row>
